--- a/tabelas_classes_excel/Tabela_3-13_O_Mago.xlsx
+++ b/tabelas_classes_excel/Tabela_3-13_O_Mago.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A283"/>
+  <dimension ref="A1:A282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -1037,12 +1037,6 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr"/>
-    </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
@@ -1057,9 +1051,6 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-    </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
@@ -1067,9 +1058,6 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-    </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
@@ -1077,9 +1065,6 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr"/>
-    </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
@@ -1087,9 +1072,6 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" t="inlineStr"/>
-    </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
@@ -1139,9 +1121,6 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" t="inlineStr"/>
-    </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
@@ -1303,9 +1282,6 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" t="inlineStr"/>
-    </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
@@ -2362,9 +2338,6 @@
           <t>de ataque.</t>
         </is>
       </c>
-    </row>
-    <row r="283">
-      <c r="A283" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2377,7 +2350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L274"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2430,31 +2403,6 @@
           <t>C7</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>C8</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2466,78 +2414,103 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bônus Base</t>
+          <t>Nível</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bônus Base de Ataque</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fortitude</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Reflexos</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Vontade</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Especial</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Nível</t>
+          <t>1°</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>de Ataque Fortitude Reflexos Vontade Especial</t>
+          <t>+0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+0</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>+0</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Invocar familiar, escrever pergaminho 3 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1°</t>
+          <t>2°</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>+0</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>+0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+0</t>
-        </is>
-      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Invocar familiar, escrever pergaminho</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>- 4 2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2°</t>
+          <t>3°</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2547,12 +2520,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>+0</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+0</t>
+          <t>+1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2562,66 +2535,46 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>- 4 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3°</t>
+          <t>4°</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>+2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>- 4 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>4°</t>
+          <t>5°</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2646,66 +2599,46 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>Talento Adicional 4 3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5°</t>
+          <t>6°</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>+3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>+1</t>
-        </is>
-      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>+2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talento Adicional</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>- 4 3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6°</t>
+          <t>7°</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2730,29 +2663,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t>- 4 4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>7°</t>
+          <t>8°</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2767,29 +2690,19 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>- 4 4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>8°</t>
+          <t>9°</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2799,12 +2712,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>+2</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2814,29 +2727,19 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>- 4 4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>9°</t>
+          <t>10°</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2851,29 +2754,19 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>+6</t>
+          <t>+7</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>Talento Adicional 4 4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10°</t>
+          <t>11°</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2898,66 +2791,46 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talento Adicional</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>- 4 4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11°</t>
+          <t>12°</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6/+1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>+3</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>+8</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>- 4 4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>12°</t>
+          <t>13°</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2982,29 +2855,19 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>- 4 4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>13°</t>
+          <t>14°</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>+6/+1</t>
+          <t>+7/+2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3019,29 +2882,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>- 4 4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14°</t>
+          <t>15°</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3051,12 +2904,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3066,29 +2919,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>Talento Adicional 4 4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>15°</t>
+          <t>16°</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>+7/+2</t>
+          <t>+8/+3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -3103,29 +2946,19 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talento Adicional</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>- 4 4</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>16°</t>
+          <t>17°</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3145,61 +2978,51 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>+10 -</t>
+          <t>+10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>- 4 4</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>17°</t>
+          <t>18°</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>+8/+3</t>
+          <t>+9/+4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>+5</t>
+          <t>+6</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>+10 -</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>- 4 4</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>18°</t>
+          <t>19°</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3219,29 +3042,24 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>+11 -</t>
+          <t>+11</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t>- 4 4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>19°</t>
+          <t>20°</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>+9/+4</t>
+          <t>+10/+5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3256,2574 +3074,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>+11 -</t>
+          <t>+12</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>20°</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>+10/+5</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>+6</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>+12 Talento Adicional</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>impede que partilhem das mesmas motivações dos outros aventureiros, sejam</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>um mago de guilda menospreze um c</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>nobres ou vilões.</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>com um eremita, não pode negar a</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Características: A força de um mago reside na sua magia; todo o restante é</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Raças: Os humanos estudam a</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>secundário. Ele aprende novas magias conforme estuda e adquire experiência, e</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>sede de poder ou simplesmente inc</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>também é capaz de aprender com outros magos. Além disso, com o tempo, um mago</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>a ser práticos e inovadores, cria</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>aprende a manipular suas magias para que tenham um alcance maior, funcionem</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>criativo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>melhor ou de alguma outra forma sejam mais eficazes.</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Os elfos são fascinados pela</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Alguns magos preferem se especializar em certos tipos de magia. Essa especia-</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>à arte. Os magos elfos se conside</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>lização torna o conjurador mais poderoso na área escolhida, mas impede que ele</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>carando-a como um mistério maravi</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>tenha acesso a algumas magias fora de seu campo de estudo. Veja Especialização</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>pragmáticos, que a enxergam como</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>em Escola.</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>A magia de ilusão é assimila</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Um mago pode invocar um familiar, um pequeno animal mágico que o serve.</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>especialista nessa escola é natur</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Para alguns magos, seu familiar é seu único amigo genuíno.</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>dessa raça. Os magos gnomos que n</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Tendência: De modo geral, os magos demonstram uma inclinação para a Ordem</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>mas não sofrem nenhum estigma esp</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>em detrimento do Caos, pois o estudo da magia recompensa os disciplinados. No</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Os magos meio-elfos sentem a</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>entanto, os ilusionistas e transmutadores são, respectivamente, mestres do engodo</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>de conquistar e entender. Alguns</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>e da transformação. Estes preferem o Caos à Ordem.</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Os magos anões e halflings s</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Religião: Em geral, os magos reverenciam Boccob (deus da magia). Alguns, em</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>o estudo da magia. Os magos meio-</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>especial os necromantes ou simplesmente os mais reclusos, preferem Wee Jas (deusa</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>indivíduos com inteligência sufic</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>da magia e da morte). Os necromantes Maus são conhecidos por adorarem Nerull</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Os drow (elfos malignos subt</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>(deus da morte). Quase sempre, os magos são mais devotados aos seus estudos que</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>é bem rara entre os humanóides se</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>ao seu lado espiritual.</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Outras Classes: Os magos est</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>História: Os magos se consideram camaradas ou rivais. Mesmo os magos de</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>classes. Eles preferem conjurar s</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>culturas ou tradições arcanas diferentes possuem muito em comum, porque todos se-</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>poderosos, “aprimorar magicamente</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>guem as mesmas leis pré-estabelecidas da magia. Diferente dos guerreiros ou ladinos,</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>contar com a magia divina de um c</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>os magos se consideram membros de um grupo distinto, embora variado. Em terras</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>(como os feiticeiros, ladinos e b</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>civilizadas, onde estudam em academias, escolas ou guildas, os magos costumam se</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>costumam julgá-los.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>identificar de acordo com sua participação nessas organizações formais. Ainda que</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Função: A função do mago dep</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>ria compartilhe funções semelhant</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Entretanto, eles também não sabem u</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MAGIAS ARCANAS E ARMADURAS</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>cisam adquirir treinamento com o talent</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Os magos e os feiticeiros não sabem usar armaduras com eficiência. Mas, ou selecionar uma classe (como guerreiro)</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>se desejarem, eles podem tentar usá-las de qualquer forma (mesmo que se características de classe. Um bardo que utiliz</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>sintam desconfortáveis) e obter os benefícios do equipamento com um trei- que uma armadura leve ou qualquer tipo de es</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>namento adequado (com os talentos Usar Armadura – leve, média e pesada chance de falha de magia arcana, mesmo que tenh</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>– ou o talento Usar Escudo) ou se tomando multiclasse e selecionando uma adequado ou Usar Escudos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>classe que lhes permita usar armaduras (consulte Personagens Multiclasse no</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Quando a magia não possui component</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>final desse capitulo). O uso da armadura, mesmo para um mago ou feiticeiro arcanos são capazes de conjurá-la usando ar</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>treinado, ainda pode interferir com a conjuração de suas magias arcanas.</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>magias podem ser conjuradas mesmo se as</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>A maioria dos personagens tem dificuldades em conjurar magias arcanas amarradas ou se ele estiver preso na manobr</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>enquanto utilizam armaduras ou carregam escudos (consulte Falha de Magia Concentração ainda sejam aplicados normalment</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Arcana). A armadura restringe os gestos complicados necessários para conjurar metamágico Magia Sem Cestos permite que</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>qualquer magia que tenha um componente gestual (a maioria). Para descobrir jure uma magia sem o componente gestual, ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>a chance de falha de magia arcana para os magos ou feiticeiros que utilizam os da magia em +1. Esse talento oferece um</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>diversos tipos de armadura, consulte a Tabela 7-6: Armaduras e Escudos.</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>arcanas usando armaduras e ignorando a</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Por outro lado, os bardos sabem usar adequadamente uma armadura leve Consulte o Capitulo 5: Talentos, para obter</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>e ainda ignoram a chance de falha de magia arcana para essas armaduras.</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>metamágicos, como Magia Sem Gestos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>classes de conjuradores, com uma enorme abrangência de opções para neutralizar</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>para os testes de resistência contr</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>seus inimigos. A maioria dos magos fornece auxílio essencial aos seus companheiros</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>modificador de Inteligência do mago</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>com suas magias, enquanto outros se concentram em adivinhação e outras facetas</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Semelhante aos demais conjurad</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>das artes arcanas.</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>uma quantidade limitada de magias d</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>se encontra na Tabela 3-13:0 Mago.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>INFORMAÇÕES DE JOGO</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>um valor elevado de Inteligência (c</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>e Magias Adicionais).</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Os magos possuem as seguintes estatísticas de jogo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Habilidades: A Inteligência determina a magia mais poderosa que um mago é</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Diferente de um bardo ou feiti</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>capaz de conjurar, a quantidade de magias disponíveis a cada dia e a dificuldade</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>tidade il</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>para resistir às suas magias (consulte Magias, a seguir). Um valor elevado</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>de Destreza será útil, pois fornecerá um bônus maior na Classe de</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Mialee</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Armadura, já que os magos não costumam usar armaduras. Um</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>valor elevado de Constituição concede mais pontos de vida ao</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>personagem, recurso que a classe não possui.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Tendência: Qualquer uma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Dado de Vida: d4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Perícias de Classe</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>As perícias de classe de um mago (e a habilidade chave</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>para cada perícia) são: Concentração (Con), Conhecimento</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>(qualquer perícia, escolhida individualmente) (Int), Decifrar</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Escrita (Int), Identificar Magia (Int), Ofícios (Int), Profissão</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>(Sab). Consulte o Capítulo 4: Perícias para obter as descrições</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>f</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>das perícias.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Pontos de Perícia no 1° nível: (2 + modificador de</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>se</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Inteligência) x 4.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Pontos de Perícia a cada nível subseqüente: 2 + modi-</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>rec</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>ficador de Inteligência.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>cio</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>mág</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Características da Classe</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Cri</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Usar Armas e Armaduras: Os magos sabem usar</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>as seguintes armas: clava, adaga, besta pesada, besta</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>15°</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>leve e bordão, mas não sabem usar nenhum tipo de</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Esse</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>armadura ou escudos. As armaduras de qualquer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>lento</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>tipo prejudicam os gestos arcanos de um mago,</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>o que pode fazer suas magias que tenham</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>componentes gestuais fracassarem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Magias: Um mago conjura magias ar-</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>canas (o mesmo tipo das magias disponíveis</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>para os feiticeiros e bardos) da lista de magias</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>de feiticeiro/mago. Ele deve escolher e preparar suas</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>magias com antecedência (veja a seguir).</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Para aprender, preparar ou conjurar uma magia, um</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>mago deve ter uma pontuação em Inteligência igual</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>ou superior a 10 + o nível da magia (Int 10 para</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>magias de nível 0, Int 11 para magias de</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>1° nível, etc.). A Classe de Dificuldade</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>grimório diariam</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>que não pertencem a nenhuma dessas escola</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>ESPECIALIZAÇÃO EM ESCOLA</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Universais.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>As magias são divididas em oito grupos distintos, chamados de escolas</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Abjuração: Magias de proteção, bloque</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>de magia; cada escola é definida por um tema comum, como a ilusão ou em Abjuração é chamado de abjurador.</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>a necromancia. Se desejar, um mago pode se especializar em uma escola</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Adivinhação: Magias que revelam infor</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>de magia (veja a seguir). A especialização permite que um mago conjure Adivinhação é chamado de adivinho. Diferente dos</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>magias adicionais da escola selecionada – no entanto, ele nunca será capaz adivinho precisa abandonar somente uma escol</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>de aprender ou conjurar as magias de algumas escolas, Essencialmente, o</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Conjuração: Magias que invocam criatu</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>mago obtém um domínio excepcional sobre uma escola negligenciando o em Conjuração é chamado de invocador.</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>estudo de outras.</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Encantamento: Magias que fornecem alg</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>A cada dia, um mago especialista consegue preparar uma magia adicio- concedem poder sobre outras criaturas para o</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>nal de cada nível da escola selecionada. Ele também recebe +2 de bônus em Encantamento é chamado de encantador.</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>testes de identificar Magia para aprender magias que pertençam à sua escola</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Evocação: Magias que manipulam energi</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>predileta (veja Adicionando Magias ao Grimório de um Mago).</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Um especialista em Evocação é chamado de</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>O mago precisa decidir se tornar um especialista e determinar sua escola</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Ilusão: Magias que alteram a percepçã</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>de especialização no 1° nível. Nesse momento, ele desistirá de duas outras especialista em Ilusão é chamado de ilusioni</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>escolas de magia (a menos que tenha escolhido se especializar em Adivi-</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Necromancia: Magias que manipulam, cr</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>nhação; veja a seguir) que se tornarão sua escolas proibidas. Por exemplo, vital. Um especialista em Necromancia é cham</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>caso o mago decida se especializar em Evocação, ele poderia abandonar as</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Transmutação: Magias que transformam</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>escolas encantamento e necromancia ou abjuração e transmutação. Nenhum suas propriedades de forma sutil. Um especialist</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>mago poderá desistir da escola Adivinhação para atender a esse requisito. As mado de transmutador.</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>magias das escolas proibidas nunca estarão disponíveis para o mago e ele</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Universal: Não se trata de uma escola</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>jamais poderá conjurá-las, nem mesmo através de pergaminhos ou varinhas. qualquer mago pode aprender. Um mago não pode</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>É impossível alterar a especialização ou as escolas proibidas posteriormente. como sua escola especializada ou como uma</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>As oito escolas de magia arcana são: Abjuração, Adivinhação, Conjuração,</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Encantamento, Evocação, Ilusão, Necromancia e Transmutação. As magias</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Magias Arcanas). Ele não é capaz de preparar nenhuma magia que não esteja regis-</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Conforme um monge adquire e</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>trada em seu grimório, com exceção de ler magias, que qualquer mago consegue</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>e seu potencial chi aumentam, co</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>preparar de memória.</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>vezes, sobre os demais.</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Um mago inicial de 1° nível terá um grimório contendo todas as magias de</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Tendência: O treinamento de</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>nível 0 (exceto as de magias de sua(s) escola(s) proibida(s), para os especialistas;</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Somente os personagens Leais são</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>consulte Especialização em Escola), mais 3 magias de 1° nível à escolha do jogador.</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Religião: O treinamento de</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Para cada ponto de bônus no modificador de Inteligência do mago (veja a Tabela</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>pectivo e possui uma conexão ínt</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>1-1: Modificadores de Habilidade e Magias Adicionais), o grimório terá uma magia</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>precisa de clérigos ou deuses. N</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>de 1° nível adicional, à escolha do jogador. A cada nível de mago, o personagem</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>dos monges, levando-os a meditar</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>inclui 2 novas magias de qualquer nível a que tenha acesso (baseado em seu novo</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>deuses que podem ser adorados pe</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>nível na classe) em seu grimório. Por exemplo, quando um mago atinge o 5° nível,</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>St. Cuthbert (deus da retribuiçã</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>ele pode escolher duas magias novas de 3° nível, uma de 1° nível e uma de 3° nível</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>História: Um monge costuma</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>ou qualquer combinação de duas magias entre o 1° e 3° níveis e adicioná-las ao</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>ao monastério ainda criança, dep</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>seu grimório. O mago também pode, a qualquer momento, adicionar as magias</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>como alimentá-los ou como recomp</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>encontradas no grimório de outros magos (veja Adicionando Magias ao Grimório</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>pela organização. A vida no mona</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>de um Mago).</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>abandona, ele não terá um víncul</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Nas grandes cidades, os mes</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Conjunto Inicial para Mago Elfo</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>arte aos interessados e dignos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Armadura: Nenhuma (9 m de deslocamento).</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>desprezo seus primos dos monasté</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Armas: Bordão (1d6/1d6, dec.x 2, 2 kg, duas mãos, concussão).</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Um monge pode ter um víncul</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Besta Leve (1d8, dec. 19-20/ x 2, 24 m, 2 kg, perfurante).</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>o mestre que o ensinou, com a tr</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Seleção de Perícias: Escolha uma quantidade de graduações de perícias igual</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>todas essas coisas. Alguns monge</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>a 2 + modificador de Inteligência.</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>seu caminho para o desenvolvimen</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Os monges reconhecem uns ao</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Perícia</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Graduação</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Habilidade</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Armadura</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>da população. Eles desenvolvem a</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Concentração</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Con</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>entre si para comprovar quem det</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Raças: Os monastérios costu</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Decifrar Escrita</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Int</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>humanos, que os incorporaram em</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Furtividade (oc)</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Des</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>quase todos os monges são humano</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Observar (oc)</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Sab</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>entre eles. Os elfos são perfeit</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Conhecimento (arcano)</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Int</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>um interesse, arte ou disciplina</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Esconder-se (oc)</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Des</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>rem monges. A tradição dos monge</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>e os halflings costumam ser nôma</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Identificar Magia</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Int</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>portanto é muito difícil que os</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Procurar (oc)</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Int</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>–</t>
-        </is>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>Os humanóides selvagens não</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>para que os monges consigam trei</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Talento: Resistência.</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>criança abandonada ou órfã de um</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Especialização de Escola: Nenhuma.</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>monastério ou adotada por um mes</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Grimório: Todas as magias de nível 0; enfeitiçar pessoas, invocar criaturas I e</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>como drows têm uma pequena, poré</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>sono; escolha mais uma dessas magias para cada ponto de bônus de Inteligência (se</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Outras Classes: Os monges s</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>houver): causar medo, leque cromático, mísseis mágicos e imagem silenciosa.</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>motivações ou perícias dos membr</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>Equipamento: Mochila com cantil, um dia de rações de viagem, saco de dormir,</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>a colaborar com os demais e são</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>saco, pederneira e isqueiro. Dez velas, porta-mapas, três páginas de pergaminho,</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>Função: O monge é mais efic</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>tinta, caneta tinteiro. Bolsa de componentes de magia, grimório. Caixa com 10</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>sua velocidade para entrar e sai</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>virotes para besta.</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>batalhas prolongadas. Ele também</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>Dinheiro: 3d6 PO.</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>concentra suas perícias na furti</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>INFORMAÇÕES DE JOGO</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>MONGE</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>Os monges possuem as seguin</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>Os monastérios estão espalhados em todo o mundo – pequenos mosteiros</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>Habilidades: A Sabedoria ap</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>fechados, habitados por monges que buscam alcançar a própria perfeição através</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>monge. A Destreza oferece uma de</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>da ação e da contemplação. Eles treinam para serem guerreiros versáteis, capazes</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>classe para um monge sem armadur</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>de lutar sem armas ou armaduras. Os habitantes dos monastérios comandados por</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>desarmado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>mestres bondosos servem como protetores da população local. Preparados para o</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>Tendência: Leal e Bom, Leal</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>combate, mesmo descalços e trajando roupas simples, os monges são capazes de</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>Dado de Vida: d8.</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>viajar incógnitos entre a população, capturando bandidos, líderes guerreiros e nobres</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>corruptos de surpresa. Por outro lado, os monastérios liderados por mestres malignos</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>Perícias de Classe</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>controlam os arredores através do medo, como o império de um governante maligno.</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>As perícias de classe de um</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>Os monges malignos são ideais como espiões, infiltradores e assassinos.</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>Acrobacia (Des), Arte da Fuga (D</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>É improvável que um determinado monge se preocupe em proteger os cam-</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>cimento (arcano) (Int), Conhecim</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>poneses ou acumular riquezas. Ele se preocupa essencialmente em aperfeiçoar sua</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>(Des), Escalar (For), Esconder-s</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>arte e, através disso, alcançar a perfeição pessoal. Seu objetivo é atingir um estado</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>(Sab), Ofícios (Int), Ouvir (Sab</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>superior ao reino dos mortais.</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>(Sab). Consulte o Capítulo 4: Pe</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Aventuras: Os monges encaram as aventuras como desafios pessoais. Eles não</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Pontos de Perícia no 1° nív</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>costumam ser exibicionistas, mas gostam de colocar suas habilidades à prova contra</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Pontos de Perícia a cada ní</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>os obstáculos que encontram em seu caminho. Eles não almejam a riqueza material,</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>cia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>mas buscam qualquer coisa capaz de ajudá-los a aperfeiçoar sua arte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Características: A característica principal do monge é sua capacidade de lutar</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Características da Classe</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>desarmado e sem armadura. Graças ao seu rigoroso treinamento, ele pode atacar</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Usar Armas e Armaduras: Os</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>com a mesma eficácia dos personagens armados – e mais rápido que um guerreiro</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>e algumas armas especiais, que f</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>com uma espada.</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>monge sabe usar são: clava, best</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Ainda que os monges não conjurem magias, eles possuem uma mágica própria.</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>kama, nunchaku, bordão, sai, shu</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Canalizando uma sutil energia, chamada chi, eles são capazes de realizar façanhas</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Equipamento para obter a descriç</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>incríveis. A proeza mais conhecida dos monges é a habilidade de atordoar um ini-</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Os monges não sabem usar ne</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>migo com um golpe desarmado. Um monge também desenvolve uma percepção</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>dos poderes especiais do monge e</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>quase sobrenatural que lhe permite se esquivar de ataques, mesmo que não tenha</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>usando uma armadura, um escudo o</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>percebido a ameaça conscientemente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>monge perde seu bônus de Sabedoria na CA, além do seu movimento rápido e sua</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Quando utiliza</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>habilidade rajada de golpes.</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>de Força (e não se</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>Bônus na CA (Ext): Um monge é altamente treinado para se esquivar de golpes</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>para todos os a</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>e desenvolve um sexto sentido que lhe permite evitar ataques inesperados.</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>ou duas</t>
-        </is>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>Quando estiver sem armadura e portando uma carga leve ou inferior, o</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>espe</t>
-        </is>
-      </c>
-    </row>
-    <row r="234">
-      <c r="A234" t="inlineStr">
-        <is>
-          <t>monge adiciona seu bônus de Sabedoria (se houver) na sua Classe</t>
-        </is>
-      </c>
-    </row>
-    <row r="235">
-      <c r="A235" t="inlineStr">
-        <is>
-          <t>de Armadura. Além disso, ele recebe +1 de bônus na CA no</t>
-        </is>
-      </c>
-    </row>
-    <row r="236">
-      <c r="A236" t="inlineStr">
-        <is>
-          <t>5° nível. Esse bônus aumenta em 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="inlineStr">
-        <is>
-          <t>ponto a cada 5 níveis subseqüentes</t>
-        </is>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="inlineStr">
-        <is>
-          <t>na classe (+2 no 10°, +3 no 15° e</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="inlineStr">
-        <is>
-          <t>+4 no 20° nível).</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="inlineStr">
-        <is>
-          <t>Esses bônus na CA são aplica-</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>dos mesmo contra ataques de toque</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr">
-        <is>
-          <t>ou quando o monge estiver surpreso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="inlineStr">
-        <is>
-          <t>Ele perde esses bônus quando estiver</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" t="inlineStr">
-        <is>
-          <t>imobilizado ou indefeso, quando usar</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" t="inlineStr">
-        <is>
-          <t>qualquer armadura, qualquer escudo ou</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>portar uma carga média ou pesada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr">
-        <is>
-          <t>Rajada de Golpes (Ext): Quando não</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>estiver usando armadura, um monge pode</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>desferir uma rajada de golpes sacrificando</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>parte da sua precisão. Ao fazê-lo, ele recebe um</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>ataque adicional na rodada, usando seu bônus</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>de ataque mais elevado, mas todos os ataques</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>realizados nessa rodada sofrem -2 de penali-</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>dade. Os bônus base de ataques modificados</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>se encontram na Tabela 3-14: O Monge. Essa</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>penalidade é aplicada durante uma rodada</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>completa, portanto afeta qualquer ataque de</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>oportunidade que o monge execute antes de</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>sua próxima ação. Quando o monge alcançar</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>o 5° nível, a penalidade é reduzida para -1</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>e desaparece no 9° nível. Para utilizar essa</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>habilidade, o monge precisa usar uma ação</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>de ataque total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>Quando desfere uma rajada de golpes,</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>um monge somente conseguirá utilizar ata-</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>ques desarmados ou as armas especiais de sua</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>classe (kama, nunchaku, bordão, sai, shuriken</t>
-        </is>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>ou siangham). Ele é capaz de golpear intercalando</t>
-        </is>
-      </c>
-    </row>
-    <row r="269">
-      <c r="A269" t="inlineStr">
-        <is>
-          <t>ataques desarmados e armas especiais de monge,</t>
-        </is>
-      </c>
-    </row>
-    <row r="270">
-      <c r="A270" t="inlineStr">
-        <is>
-          <t>conforme desejar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="271">
-      <c r="A271" t="inlineStr">
-        <is>
-          <t>Por exemplo, Ember, uma monja de 6° nível, poderia</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" t="inlineStr">
-        <is>
-          <t>desferir um ataque desarmado com +3 de bônus de ataque e</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>um ataque com sua arma especial de monge com +3 de bônus</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Ember</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>de ataque.</t>
+          <t>Talento Adicional 4 4</t>
         </is>
       </c>
     </row>
